--- a/Projects/Tobias Harris.xlsx
+++ b/Projects/Tobias Harris.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91E6509-8455-8348-9386-876485717861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970F2BAF-EEC6-034A-B0CF-D7127316F4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="11" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="54580" yWindow="620" windowWidth="14060" windowHeight="21000" firstSheet="1" activeTab="5" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -10094,7 +10094,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>146</v>
       </c>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AG2" s="3"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>150</v>
       </c>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="AG3" s="3"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>150</v>
       </c>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AG4" s="4"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>150</v>
       </c>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="AG5" s="4"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>153</v>
       </c>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="AG6" s="3"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>154</v>
       </c>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="AG7" s="3"/>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>155</v>
       </c>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="AG8" s="3"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>155</v>
       </c>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="AG9" s="4"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>155</v>
       </c>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AG10" s="4"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>157</v>
       </c>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="AG11" s="3"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>158</v>
       </c>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="AG12" s="3"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>158</v>
       </c>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="AG13" s="4"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>158</v>
       </c>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AG14" s="4"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>160</v>
       </c>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AG15" s="3"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>160</v>
       </c>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="AG16" s="4"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>160</v>
       </c>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="AG17" s="4"/>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>162</v>
       </c>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="AG18" s="3"/>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>163</v>
       </c>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="AG19" s="3"/>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>164</v>
       </c>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="AG20" s="3"/>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>165</v>
       </c>

--- a/Projects/Tobias Harris.xlsx
+++ b/Projects/Tobias Harris.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970F2BAF-EEC6-034A-B0CF-D7127316F4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B88C7D-3129-0243-8073-50E29FBCD87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="54580" yWindow="620" windowWidth="14060" windowHeight="21000" firstSheet="1" activeTab="5" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="54580" yWindow="620" windowWidth="14060" windowHeight="21000" firstSheet="3" activeTab="4" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -14651,19 +14651,19 @@
     <col min="6" max="6" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.5" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -16730,7 +16730,7 @@
     <col min="13" max="13" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -16819,7 +16819,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>146</v>
       </c>
@@ -16894,7 +16894,7 @@
       </c>
       <c r="Y2" s="3"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>150</v>
       </c>
@@ -16969,7 +16969,7 @@
       </c>
       <c r="Y3" s="3"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>150</v>
       </c>
@@ -17044,7 +17044,7 @@
       </c>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>150</v>
       </c>
@@ -17119,7 +17119,7 @@
       </c>
       <c r="Y5" s="4"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>153</v>
       </c>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="Y6" s="3"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>154</v>
       </c>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="Y7" s="3"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>155</v>
       </c>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="Y8" s="3"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>155</v>
       </c>
@@ -17419,7 +17419,7 @@
       </c>
       <c r="Y9" s="4"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>155</v>
       </c>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="Y10" s="4"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>157</v>
       </c>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="Y11" s="3"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>158</v>
       </c>
@@ -17644,7 +17644,7 @@
       </c>
       <c r="Y12" s="3"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>158</v>
       </c>
@@ -17719,7 +17719,7 @@
       </c>
       <c r="Y13" s="4"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>158</v>
       </c>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="Y14" s="4"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>160</v>
       </c>
@@ -17869,7 +17869,7 @@
       </c>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>160</v>
       </c>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="Y16" s="4"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>160</v>
       </c>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="Y17" s="4"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>162</v>
       </c>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>163</v>
       </c>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>164</v>
       </c>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>165</v>
       </c>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>166</v>
       </c>
@@ -18631,24 +18631,24 @@
     <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="23" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.2">
@@ -18746,7 +18746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>146</v>
       </c>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="AE2" s="3"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>150</v>
       </c>
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AE3" s="3"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>150</v>
       </c>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="AE4" s="4"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>150</v>
       </c>
@@ -19118,7 +19118,7 @@
       </c>
       <c r="AE5" s="4"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>153</v>
       </c>
@@ -19211,7 +19211,7 @@
       </c>
       <c r="AE6" s="3"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>154</v>
       </c>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="AE7" s="3"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>155</v>
       </c>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="AE8" s="3"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>155</v>
       </c>
@@ -19490,7 +19490,7 @@
       </c>
       <c r="AE9" s="4"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>155</v>
       </c>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="AE10" s="4"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>157</v>
       </c>
@@ -19676,7 +19676,7 @@
       </c>
       <c r="AE11" s="3"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>158</v>
       </c>
@@ -19769,7 +19769,7 @@
       </c>
       <c r="AE12" s="3"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>158</v>
       </c>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="AE13" s="4"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>158</v>
       </c>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="AE14" s="4"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>160</v>
       </c>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="AE15" s="3"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>160</v>
       </c>
@@ -20141,7 +20141,7 @@
       </c>
       <c r="AE16" s="4"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>160</v>
       </c>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AE17" s="4"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>162</v>
       </c>
@@ -20327,7 +20327,7 @@
       </c>
       <c r="AE18" s="3"/>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>163</v>
       </c>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="AE19" s="3"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>164</v>
       </c>
@@ -20513,7 +20513,7 @@
       </c>
       <c r="AE20" s="3"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>165</v>
       </c>
